--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>10116 SEÑOR NAZARENO CAUTIVO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.644248</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.920146</v>
-      </c>
-      <c r="I2" t="n">
-        <v>482</v>
-      </c>
-      <c r="J2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.644248</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.920146</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>202 SAN GABRIEL ARCANGEL</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.6984</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.9054</v>
-      </c>
-      <c r="I3" t="n">
-        <v>342</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.6984</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.9054</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>203 PASITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.70517</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.90571</v>
-      </c>
-      <c r="I4" t="n">
-        <v>369</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.70517</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.90571</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>208 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.70183</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.89802</v>
-      </c>
-      <c r="I5" t="n">
-        <v>258</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.70183</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.89802</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>209 GOTITAS DE AMOR</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.71166</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.91750999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>334</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.71166</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.91751</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>235 DORIS DAY FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.708189</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.900502</v>
-      </c>
-      <c r="I7" t="n">
-        <v>252</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.708189</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.900502</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>10104 JUAN FANNING GARCIA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.70459</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.90543</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1054</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.70459</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.90543</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>10106 JUAN MANUEL ITURREGUI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.70284</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.90352</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2869</v>
-      </c>
-      <c r="J9" t="n">
-        <v>117</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.70284</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.90352</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2869</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>10109</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.707194</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.91242200000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>403</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.707194</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.912422</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>10110 SARA ANTONIETA BULLON LAMADRID</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.69938</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.90315</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J11" t="n">
-        <v>87</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.69938</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.90315</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>10111 NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.6975</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.9054</v>
-      </c>
-      <c r="I12" t="n">
-        <v>494</v>
-      </c>
-      <c r="J12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.6975</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.9054</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>10112 SAN MARTIN DE PORRES VELASQUEZ</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.69983</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.91367</v>
-      </c>
-      <c r="I13" t="n">
-        <v>621</v>
-      </c>
-      <c r="J13" t="n">
-        <v>28</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.69983</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.91367</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>11036 27 DE DICIEMBRE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.70431</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.90685000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J14" t="n">
-        <v>62</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.70431</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.90685</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>11037 ANTONIA ZAPATA JORDAN</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.702228</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.898726</v>
-      </c>
-      <c r="I15" t="n">
-        <v>523</v>
-      </c>
-      <c r="J15" t="n">
-        <v>23</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.702228</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.898726</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>11230</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.615431</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.930329</v>
-      </c>
-      <c r="I16" t="n">
-        <v>322</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.615431</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.930329</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>11239 CRISTO DE PACHACAMILLA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-6.70321</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.91696</v>
-      </c>
-      <c r="I17" t="n">
-        <v>590</v>
-      </c>
-      <c r="J17" t="n">
-        <v>22</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.70321</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.91696</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SAN MARTIN</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-6.70123</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.91670999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>680</v>
-      </c>
-      <c r="J18" t="n">
-        <v>36</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.70123</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.91671</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-6.70126</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.90333</v>
-      </c>
-      <c r="I19" t="n">
-        <v>678</v>
-      </c>
-      <c r="J19" t="n">
-        <v>44</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.70126</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.90333</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-6.70087</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.90557</v>
-      </c>
-      <c r="I20" t="n">
-        <v>265</v>
-      </c>
-      <c r="J20" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.70087</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.90557</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>11136 SEÑOR DE SICAN</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-6.478536</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.82201000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>317</v>
-      </c>
-      <c r="J21" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-6.478536</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.82201</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>10138 AUGUSTO CASTILLO MURO SIME</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-6.612432</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.894582</v>
-      </c>
-      <c r="I22" t="n">
-        <v>784</v>
-      </c>
-      <c r="J22" t="n">
-        <v>40</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-6.612432</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.894582</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>10132 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-6.5487</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.864</v>
-      </c>
-      <c r="I23" t="n">
-        <v>791</v>
-      </c>
-      <c r="J23" t="n">
-        <v>36</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.5487</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.864</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>10141 - 7 DE NOVIEMBRE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-6.598827</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.933924</v>
-      </c>
-      <c r="I24" t="n">
-        <v>560</v>
-      </c>
-      <c r="J24" t="n">
-        <v>31</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-6.598827</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.933924</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>10781 CRISTO REDENTOR</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-6.625524</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-79.865038</v>
-      </c>
-      <c r="I25" t="n">
-        <v>310</v>
-      </c>
-      <c r="J25" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-6.625524</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-79.865038</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>10168 SAN PEDRO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-6.50154</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.00922</v>
-      </c>
-      <c r="I26" t="n">
-        <v>708</v>
-      </c>
-      <c r="J26" t="n">
-        <v>38</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-6.50154</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.00922</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>10160 ROSA DE AMERICA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-6.509</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.9649</v>
-      </c>
-      <c r="I27" t="n">
-        <v>809</v>
-      </c>
-      <c r="J27" t="n">
-        <v>34</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-6.509</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.9649</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>10163 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-6.5223</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-79.9453</v>
-      </c>
-      <c r="I28" t="n">
-        <v>367</v>
-      </c>
-      <c r="J28" t="n">
-        <v>28</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-6.5223</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.9453</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>10158 JULIO C. TELLO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-6.514743</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-79.961384</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1523</v>
-      </c>
-      <c r="J29" t="n">
-        <v>66</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-6.514743</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-79.961384</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>10888 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-6.518577</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-79.926362</v>
-      </c>
-      <c r="I30" t="n">
-        <v>448</v>
-      </c>
-      <c r="J30" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-6.518577</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.926362</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>10991</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-6.499594</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-79.955264</v>
-      </c>
-      <c r="I31" t="n">
-        <v>274</v>
-      </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-6.499594</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-79.955264</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>11094 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-6.560261</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-79.94073899999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>226</v>
-      </c>
-      <c r="J32" t="n">
-        <v>12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-6.560261</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-79.940739</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>11130 ARACELY QUISPE NEIRA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-6.69876</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-79.961879</v>
-      </c>
-      <c r="I33" t="n">
-        <v>316</v>
-      </c>
-      <c r="J33" t="n">
-        <v>15</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-6.69876</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-79.961879</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>10164 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-6.543718</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-79.965886</v>
-      </c>
-      <c r="I34" t="n">
-        <v>532</v>
-      </c>
-      <c r="J34" t="n">
-        <v>30</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-6.543718</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-79.965886</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>10153 CARLOS DEL CASTILLO NIÑO</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-6.2113</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-79.6962</v>
-      </c>
-      <c r="I35" t="n">
-        <v>378</v>
-      </c>
-      <c r="J35" t="n">
-        <v>21</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-6.2113</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-79.6962</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>10785 PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-5.89965</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-79.74361500000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>231</v>
-      </c>
-      <c r="J36" t="n">
-        <v>14</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.89965</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-79.743615</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>10177</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-5.887</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-79.8878</v>
-      </c>
-      <c r="I37" t="n">
-        <v>440</v>
-      </c>
-      <c r="J37" t="n">
-        <v>25</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5.887</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-79.8878</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>10201</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-6.4282</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-79.8413</v>
-      </c>
-      <c r="I38" t="n">
-        <v>614</v>
-      </c>
-      <c r="J38" t="n">
-        <v>24</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-6.4282</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-79.8413</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>215 NIÑOS DEL SABER</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-6.773666</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-79.921194</v>
-      </c>
-      <c r="I39" t="n">
-        <v>266</v>
-      </c>
-      <c r="J39" t="n">
-        <v>11</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-6.773666</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-79.921194</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>10232 HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-6.476069</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-79.91486500000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>455</v>
-      </c>
-      <c r="J40" t="n">
-        <v>24</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-6.476069</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-79.914865</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>10163 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-6.5159</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-79.94459999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>432</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-6.5159</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-79.9446</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>MARIA DE LA PAZ</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-6.70005</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-79.91045</v>
-      </c>
-      <c r="I42" t="n">
-        <v>300</v>
-      </c>
-      <c r="J42" t="n">
-        <v>27</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-6.70005</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-79.91045</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>AFUL - LAMBAYEQUE</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-6.70439</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-79.90604</v>
-      </c>
-      <c r="I43" t="n">
-        <v>208</v>
-      </c>
-      <c r="J43" t="n">
-        <v>13</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-6.70439</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-79.90604</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>LAMBAYEQUE</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-6.70149</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-79.89507999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>208</v>
-      </c>
-      <c r="J44" t="n">
-        <v>21</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-6.70149</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-79.89508</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>PERUANO - ESPAÑOL</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-6.7023</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-79.90551000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>826</v>
-      </c>
-      <c r="J45" t="n">
-        <v>38</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-6.7023</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-79.90551</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>EXCELENCIA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-6.391399</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-79.82383900000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>419</v>
-      </c>
-      <c r="J46" t="n">
-        <v>26</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-6.391399</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-79.823839</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>11624 MARTIR PNP WILLIAMS WILFREDO VALDIVIESO SANTA MARIA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-6.54789</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-80.01769</v>
-      </c>
-      <c r="I47" t="n">
-        <v>487</v>
-      </c>
-      <c r="J47" t="n">
-        <v>23</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-6.54789</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-80.01769</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>INNOVA KINDER SCHOOL</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-6.69715</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-79.90946</v>
-      </c>
-      <c r="I48" t="n">
-        <v>351</v>
-      </c>
-      <c r="J48" t="n">
-        <v>37</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-6.69715</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-79.90946</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>SANTO TORIBIO DE MOGROVEJO DE MOTUPE</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-6.16161</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-79.72166</v>
-      </c>
-      <c r="I49" t="n">
-        <v>956</v>
-      </c>
-      <c r="J49" t="n">
-        <v>30</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-6.16161</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-79.72166</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>283527</t>
+          <t>283570</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10116 SEÑOR NAZARENO CAUTIVO</t>
+          <t>235 DORIS DAY FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.644248</t>
+          <t>-6.708189</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.920146</t>
+          <t>-79.900502</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>283532</t>
+          <t>283551</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>202 SAN GABRIEL ARCANGEL</t>
+          <t>208 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.6984</t>
+          <t>-6.70183</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.9054</t>
+          <t>-79.89802</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>283546</t>
+          <t>287455</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>203 PASITOS DE JESUS</t>
+          <t>215 NIÑOS DEL SABER</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.70517</t>
+          <t>-6.773666</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.90571</t>
+          <t>-79.921194</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>283551</t>
+          <t>283594</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>208 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>10106 JUAN MANUEL ITURREGUI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.70183</t>
+          <t>-6.70284</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.89802</t>
+          <t>-79.90352</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>117</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>283565</t>
+          <t>285022</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>209 GOTITAS DE AMOR</t>
+          <t>11094 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.71166</t>
+          <t>-6.560261</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.91751</t>
+          <t>-79.940739</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>283570</t>
+          <t>283565</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>235 DORIS DAY FERNANDEZ FERNANDEZ</t>
+          <t>209 GOTITAS DE AMOR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.708189</t>
+          <t>-6.71166</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.900502</t>
+          <t>-79.91751</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>283589</t>
+          <t>678500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10104 JUAN FANNING GARCIA</t>
+          <t>AFUL - LAMBAYEQUE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.70459</t>
+          <t>-6.70439</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.90543</t>
+          <t>-79.90604</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>283594</t>
+          <t>286026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10106 JUAN MANUEL ITURREGUI</t>
+          <t>10785 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.70284</t>
+          <t>-5.89965</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.90352</t>
+          <t>-79.743615</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>283607</t>
+          <t>283532</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>202 SAN GABRIEL ARCANGEL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.707194</t>
+          <t>-6.6984</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.912422</t>
+          <t>-79.9054</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>283612</t>
+          <t>283546</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10110 SARA ANTONIETA BULLON LAMADRID</t>
+          <t>203 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.69938</t>
+          <t>-6.70517</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.90315</t>
+          <t>-79.90571</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>369</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>283626</t>
+          <t>283607</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10111 NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.6975</t>
+          <t>-6.707194</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.9054</t>
+          <t>-79.912422</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>283631</t>
+          <t>285041</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10112 SAN MARTIN DE PORRES VELASQUEZ</t>
+          <t>11130 ARACELY QUISPE NEIRA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.69983</t>
+          <t>-6.69876</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.91367</t>
+          <t>-79.961879</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>283650</t>
+          <t>283928</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11036 27 DE DICIEMBRE</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.70431</t>
+          <t>-6.70087</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.90685</t>
+          <t>-79.90557</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>283688</t>
+          <t>283725</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11037 ANTONIA ZAPATA JORDAN</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.702228</t>
+          <t>-6.615431</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.898726</t>
+          <t>-79.930329</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>283725</t>
+          <t>284065</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11136 SEÑOR DE SICAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.615431</t>
+          <t>-6.478536</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.930329</t>
+          <t>-79.82201</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>317</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>283749</t>
+          <t>284541</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11239 CRISTO DE PACHACAMILLA</t>
+          <t>10781 CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.70321</t>
+          <t>-6.625524</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.91696</t>
+          <t>-79.865038</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>283768</t>
+          <t>539726</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>10163 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.70123</t>
+          <t>-6.5159</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.91671</t>
+          <t>-79.9446</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>283867</t>
+          <t>285357</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>10153 CARLOS DEL CASTILLO NIÑO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.70126</t>
+          <t>-6.2113</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.90333</t>
+          <t>-79.6962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>283928</t>
+          <t>745335</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>LAMBAYEQUE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.70087</t>
+          <t>-6.70149</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.90557</t>
+          <t>-79.89508</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>284065</t>
+          <t>283749</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11136 SEÑOR DE SICAN</t>
+          <t>11239 CRISTO DE PACHACAMILLA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.478536</t>
+          <t>-6.70321</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.82201</t>
+          <t>-79.91696</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>590</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>284433</t>
+          <t>283626</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10138 AUGUSTO CASTILLO MURO SIME</t>
+          <t>10111 NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.612432</t>
+          <t>-6.6975</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.894582</t>
+          <t>-79.9054</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>284452</t>
+          <t>283688</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10132 JESUS DIVINO MAESTRO</t>
+          <t>11037 ANTONIA ZAPATA JORDAN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.5487</t>
+          <t>-6.702228</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.864</t>
+          <t>-79.898726</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>523</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>284536</t>
+          <t>286776</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10141 - 7 DE NOVIEMBRE</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.598827</t>
+          <t>-6.4282</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.933924</t>
+          <t>-79.8413</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>284541</t>
+          <t>287672</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10781 CRISTO REDENTOR</t>
+          <t>10232 HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.625524</t>
+          <t>-6.476069</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.865038</t>
+          <t>-79.914865</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>284701</t>
+          <t>286677</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10168 SAN PEDRO</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.50154</t>
+          <t>-5.887</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.00922</t>
+          <t>-79.8878</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>440</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>284720</t>
+          <t>840356</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10160 ROSA DE AMERICA</t>
+          <t>EXCELENCIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.509</t>
+          <t>-6.391399</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.9649</t>
+          <t>-79.823839</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>284777</t>
+          <t>650884</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10163 JORGE BASADRE GROHMANN</t>
+          <t>MARIA DE LA PAZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.5223</t>
+          <t>-6.70005</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.9453</t>
+          <t>-79.91045</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>284819</t>
+          <t>283527</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10158 JULIO C. TELLO</t>
+          <t>10116 SEÑOR NAZARENO CAUTIVO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.514743</t>
+          <t>-6.644248</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.961384</t>
+          <t>-79.920146</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>284862</t>
+          <t>283631</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10888 SEÑOR DE LOS MILAGROS</t>
+          <t>10112 SAN MARTIN DE PORRES VELASQUEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.518577</t>
+          <t>-6.69983</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.926362</t>
+          <t>-79.91367</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>621</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>284937</t>
+          <t>284777</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>10163 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.499594</t>
+          <t>-6.5223</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.955264</t>
+          <t>-79.9453</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>285022</t>
+          <t>284862</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>11094 VIRGEN DE LA PUERTA</t>
+          <t>10888 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.560261</t>
+          <t>-6.518577</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.940739</t>
+          <t>-79.926362</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>285041</t>
+          <t>285178</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11130 ARACELY QUISPE NEIRA</t>
+          <t>10164 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.69876</t>
+          <t>-6.543718</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.961879</t>
+          <t>-79.965886</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>532</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,27 +2485,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>285178</t>
+          <t>905381</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10164 DIVINO NIÑO JESUS</t>
+          <t>SANTO TORIBIO DE MOGROVEJO DE MOTUPE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.543718</t>
+          <t>-6.16161</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.965886</t>
+          <t>-79.72166</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>956</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>285357</t>
+          <t>284536</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10153 CARLOS DEL CASTILLO NIÑO</t>
+          <t>10141 - 7 DE NOVIEMBRE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.2113</t>
+          <t>-6.598827</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.6962</t>
+          <t>-79.933924</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>560</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>286026</t>
+          <t>283768</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10785 PEDRO RUIZ GALLO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.89965</t>
+          <t>-6.70123</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.743615</t>
+          <t>-79.91671</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>680</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>286677</t>
+          <t>284452</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10132 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.887</t>
+          <t>-6.5487</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.8878</t>
+          <t>-79.864</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>791</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>286776</t>
+          <t>862273</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>INNOVA KINDER SCHOOL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.4282</t>
+          <t>-6.69715</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.8413</t>
+          <t>-79.90946</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>287455</t>
+          <t>284701</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>215 NIÑOS DEL SABER</t>
+          <t>10168 SAN PEDRO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.773666</t>
+          <t>-6.50154</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.921194</t>
+          <t>-80.00922</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>708</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>287672</t>
+          <t>747933</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10232 HORACIO ZEBALLOS GAMEZ</t>
+          <t>PERUANO - ESPAÑOL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.476069</t>
+          <t>-6.7023</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.914865</t>
+          <t>-79.90551</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>826</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>539726</t>
+          <t>284433</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10163 JORGE BASADRE GROHMANN</t>
+          <t>10138 AUGUSTO CASTILLO MURO SIME</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.5159</t>
+          <t>-6.612432</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.9446</t>
+          <t>-79.894582</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>784</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>650884</t>
+          <t>283589</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MARIA DE LA PAZ</t>
+          <t>10104 JUAN FANNING GARCIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.70005</t>
+          <t>-6.70459</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.91045</t>
+          <t>-79.90543</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>678500</t>
+          <t>283867</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFUL - LAMBAYEQUE</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.70439</t>
+          <t>-6.70126</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.90604</t>
+          <t>-79.90333</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>745335</t>
+          <t>283650</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>11036 27 DE DICIEMBRE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.70149</t>
+          <t>-6.70431</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.89508</t>
+          <t>-79.90685</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>747933</t>
+          <t>284819</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PERUANO - ESPAÑOL</t>
+          <t>10158 JULIO C. TELLO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.7023</t>
+          <t>-6.514743</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.90551</t>
+          <t>-79.961384</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>840356</t>
+          <t>283612</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EXCELENCIA</t>
+          <t>10110 SARA ANTONIETA BULLON LAMADRID</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.391399</t>
+          <t>-6.69938</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.823839</t>
+          <t>-79.90315</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3263,192 +3263,6 @@
         </is>
       </c>
       <c r="L46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>860434</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>11624 MARTIR PNP WILLIAMS WILFREDO VALDIVIESO SANTA MARIA</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-6.54789</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-80.01769</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>862273</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>INNOVA KINDER SCHOOL</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-6.69715</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-79.90946</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>905381</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>SANTO TORIBIO DE MOGROVEJO DE MOTUPE</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-6.16161</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-79.72166</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>283570</t>
+          <t>905381</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>235 DORIS DAY FERNANDEZ FERNANDEZ</t>
+          <t>SANTO TORIBIO DE MOGROVEJO DE MOTUPE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.708189</t>
+          <t>956</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.900502</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-6.16161</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.72166</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>283551</t>
+          <t>862273</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>208 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>INNOVA KINDER SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.70183</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.89802</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-6.69715</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.90946</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>287455</t>
+          <t>840356</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>215 NIÑOS DEL SABER</t>
+          <t>EXCELENCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.773666</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.921194</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-6.391399</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.823839</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>283594</t>
+          <t>747933</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10106 JUAN MANUEL ITURREGUI</t>
+          <t>PERUANO - ESPAÑOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.70284</t>
+          <t>826</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.90352</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>-6.7023</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>-79.90551</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>285022</t>
+          <t>745335</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11094 VIRGEN DE LA PUERTA</t>
+          <t>LAMBAYEQUE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.560261</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.940739</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-6.70149</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-79.89508</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>283565</t>
+          <t>678500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>209 GOTITAS DE AMOR</t>
+          <t>AFUL - LAMBAYEQUE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.71166</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.91751</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-6.70439</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.90604</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>678500</t>
+          <t>650884</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AFUL - LAMBAYEQUE</t>
+          <t>MARIA DE LA PAZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.70439</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.90604</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-6.70005</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.91045</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>286026</t>
+          <t>539726</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10785 PEDRO RUIZ GALLO</t>
+          <t>10163 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.89965</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.743615</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-6.5159</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.9446</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>283532</t>
+          <t>287672</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>202 SAN GABRIEL ARCANGEL</t>
+          <t>10232 HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.6984</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.9054</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-6.476069</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.914865</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>283546</t>
+          <t>287455</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>203 PASITOS DE JESUS</t>
+          <t>215 NIÑOS DEL SABER</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.70517</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.90571</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>-6.773666</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.921194</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>283607</t>
+          <t>286776</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.707194</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.912422</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-6.4282</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.8413</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>285041</t>
+          <t>286677</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11130 ARACELY QUISPE NEIRA</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.69876</t>
+          <t>440</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.961879</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-5.887</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.8878</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>283928</t>
+          <t>286026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>10785 PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.70087</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.90557</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-5.89965</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.743615</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>283725</t>
+          <t>285357</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>10153 CARLOS DEL CASTILLO NIÑO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.615431</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.930329</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-6.2113</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.6962</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>284065</t>
+          <t>285178</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11136 SEÑOR DE SICAN</t>
+          <t>10164 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.478536</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.82201</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-6.543718</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.965886</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>284541</t>
+          <t>285041</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10781 CRISTO REDENTOR</t>
+          <t>11130 ARACELY QUISPE NEIRA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.625524</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.865038</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-6.69876</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.961879</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>539726</t>
+          <t>285022</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10163 JORGE BASADRE GROHMANN</t>
+          <t>11094 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.5159</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.9446</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-6.560261</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.940739</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>285357</t>
+          <t>284862</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10153 CARLOS DEL CASTILLO NIÑO</t>
+          <t>10888 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.2113</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.6962</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-6.518577</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.926362</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>745335</t>
+          <t>284819</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>10158 JULIO C. TELLO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.70149</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.89508</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-6.514743</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.961384</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>283749</t>
+          <t>284777</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11239 CRISTO DE PACHACAMILLA</t>
+          <t>10163 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.70321</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.91696</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>-6.5223</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.9453</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>283626</t>
+          <t>284701</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10111 NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>10168 SAN PEDRO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.6975</t>
+          <t>708</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.9054</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>-6.50154</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-80.00922</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>283688</t>
+          <t>284541</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11037 ANTONIA ZAPATA JORDAN</t>
+          <t>10781 CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.702228</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.898726</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>-6.625524</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.865038</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>286776</t>
+          <t>284536</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10141 - 7 DE NOVIEMBRE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.4282</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.8413</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-6.598827</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.933924</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>287672</t>
+          <t>284452</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10232 HORACIO ZEBALLOS GAMEZ</t>
+          <t>10132 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.476069</t>
+          <t>791</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.914865</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-6.5487</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.864</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>286677</t>
+          <t>284433</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10138 AUGUSTO CASTILLO MURO SIME</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.887</t>
+          <t>784</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.8878</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>-6.612432</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.894582</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>840356</t>
+          <t>284065</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EXCELENCIA</t>
+          <t>11136 SEÑOR DE SICAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.391399</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.823839</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-6.478536</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.82201</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>650884</t>
+          <t>283928</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARIA DE LA PAZ</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.70005</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.91045</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-6.70087</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.90557</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>283527</t>
+          <t>283867</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10116 SEÑOR NAZARENO CAUTIVO</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.644248</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.920146</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-6.70126</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.90333</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>283631</t>
+          <t>283768</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10112 SAN MARTIN DE PORRES VELASQUEZ</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.69983</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.91367</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>-6.70123</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.91671</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>284777</t>
+          <t>283749</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10163 JORGE BASADRE GROHMANN</t>
+          <t>11239 CRISTO DE PACHACAMILLA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.5223</t>
+          <t>590</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.9453</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-6.70321</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.91696</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>284862</t>
+          <t>283725</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10888 SEÑOR DE LOS MILAGROS</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.518577</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.926362</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-6.615431</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.930329</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>285178</t>
+          <t>283688</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10164 DIVINO NIÑO JESUS</t>
+          <t>11037 ANTONIA ZAPATA JORDAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.543718</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.965886</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>-6.702228</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.898726</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>905381</t>
+          <t>283650</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTO TORIBIO DE MOGROVEJO DE MOTUPE</t>
+          <t>11036 27 DE DICIEMBRE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.16161</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.72166</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>-6.70431</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.90685</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>284536</t>
+          <t>283631</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10141 - 7 DE NOVIEMBRE</t>
+          <t>10112 SAN MARTIN DE PORRES VELASQUEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.598827</t>
+          <t>621</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.933924</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>-6.69983</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-79.91367</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>283768</t>
+          <t>283626</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>10111 NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.70123</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.91671</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>-6.6975</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.9054</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>284452</t>
+          <t>283612</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10132 JESUS DIVINO MAESTRO</t>
+          <t>10110 SARA ANTONIETA BULLON LAMADRID</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-6.5487</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.864</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>-6.69938</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.90315</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>862273</t>
+          <t>283607</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INNOVA KINDER SCHOOL</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.69715</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.90946</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-6.707194</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-79.912422</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>284701</t>
+          <t>283594</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10168 SAN PEDRO</t>
+          <t>10106 JUAN MANUEL ITURREGUI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.50154</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.00922</t>
+          <t>117</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>-6.70284</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.90352</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>747933</t>
+          <t>283589</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PERUANO - ESPAÑOL</t>
+          <t>10104 JUAN FANNING GARCIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.7023</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.90551</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>-6.70459</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.90543</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>284433</t>
+          <t>283570</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10138 AUGUSTO CASTILLO MURO SIME</t>
+          <t>235 DORIS DAY FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.612432</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.894582</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>-6.708189</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-79.900502</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>283589</t>
+          <t>283565</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10104 JUAN FANNING GARCIA</t>
+          <t>209 GOTITAS DE AMOR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.70459</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.90543</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>-6.71166</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.91751</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>283867</t>
+          <t>283551</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>208 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.70126</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.90333</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>-6.70183</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-79.89802</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>283650</t>
+          <t>283546</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>11036 27 DE DICIEMBRE</t>
+          <t>203 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.70431</t>
+          <t>369</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.90685</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>-6.70517</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-79.90571</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>284819</t>
+          <t>283532</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10158 JULIO C. TELLO</t>
+          <t>202 SAN GABRIEL ARCANGEL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.514743</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.961384</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>-6.6984</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-79.9054</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>283612</t>
+          <t>283527</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10110 SARA ANTONIETA BULLON LAMADRID</t>
+          <t>10116 SEÑOR NAZARENO CAUTIVO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.69938</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.90315</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>-6.644248</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-79.920146</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
